--- a/input/ES/scenario_parametricMatching.xlsx
+++ b/input/ES/scenario_parametricMatching.xlsx
@@ -93,7 +93,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.0492680317105201</v>
+        <v>2.0539561576818137</v>
       </c>
     </row>
     <row r="3">
@@ -101,7 +101,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.5305492567122443</v>
+        <v>1.7021624681871299</v>
       </c>
     </row>
     <row r="4">
@@ -109,7 +109,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>17.224177601355898</v>
+        <v>17.118178119543629</v>
       </c>
     </row>
     <row r="5">
@@ -117,7 +117,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>61.510864622339504</v>
+        <v>73.697198029916024</v>
       </c>
     </row>
     <row r="6">
@@ -125,7 +125,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.57690763380473997</v>
+        <v>0.88435432694592808</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/scenario_parametricMatching.xlsx
+++ b/input/ES/scenario_parametricMatching.xlsx
@@ -93,7 +93,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.0539561576818137</v>
+        <v>2.0524526698456165</v>
       </c>
     </row>
     <row r="3">
@@ -101,7 +101,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.7021624681871299</v>
+        <v>1.7149711190408228</v>
       </c>
     </row>
     <row r="4">
@@ -109,7 +109,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>17.118178119543629</v>
+        <v>17.123641410944359</v>
       </c>
     </row>
     <row r="5">
@@ -117,7 +117,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>73.697198029916024</v>
+        <v>72.937813625305722</v>
       </c>
     </row>
     <row r="6">
@@ -125,7 +125,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.88435432694592808</v>
+        <v>0.86935327554824238</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/scenario_parametricMatching.xlsx
+++ b/input/ES/scenario_parametricMatching.xlsx
@@ -101,7 +101,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.7149711190408228</v>
+        <v>1.7178722807296813</v>
       </c>
     </row>
     <row r="4">
@@ -117,7 +117,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>72.937813625305722</v>
+        <v>72.916276085778648</v>
       </c>
     </row>
     <row r="6">
@@ -125,7 +125,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.86935327554824238</v>
+        <v>0.87399340381215795</v>
       </c>
     </row>
   </sheetData>
